--- a/database/ddml-new/Services.xlsx
+++ b/database/ddml-new/Services.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kimoy\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SourceCloud\academically-app\database\ddml-new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731106F8-A8F4-4A3C-8677-E9AB718734B7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC9823F-0ADC-4A76-9DC1-BBD1B42FBB8C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{F3EA5023-54CA-45E6-862A-5E1D4864724A}"/>
+    <workbookView minimized="1" xWindow="9150" yWindow="6495" windowWidth="19995" windowHeight="7620" xr2:uid="{F3EA5023-54CA-45E6-862A-5E1D4864724A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
